--- a/diseases/d007/2000-2004.xlsx
+++ b/diseases/d007/2000-2004.xlsx
@@ -42216,7 +42216,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -43700,7 +43700,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45184,7 +45184,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -46668,7 +46668,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -48152,7 +48152,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -49636,7 +49636,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -51120,7 +51120,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -52604,7 +52604,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -54088,7 +54088,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -55572,7 +55572,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -57056,7 +57056,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -58540,7 +58540,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -60263,7 +60263,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -61747,7 +61747,7 @@
       </c>
       <c r="AJ334" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK334" t="inlineStr">
@@ -63231,7 +63231,7 @@
       </c>
       <c r="AJ342" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK342" t="inlineStr">
@@ -64715,7 +64715,7 @@
       </c>
       <c r="AJ350" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK350" t="inlineStr">
@@ -66199,7 +66199,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -67683,7 +67683,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -69167,7 +69167,7 @@
       </c>
       <c r="AJ374" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK374" t="inlineStr">
@@ -70651,7 +70651,7 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -72135,7 +72135,7 @@
       </c>
       <c r="AJ390" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK390" t="inlineStr">
@@ -73619,7 +73619,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -75103,7 +75103,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -76587,7 +76587,7 @@
       </c>
       <c r="AJ414" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK414" t="inlineStr">

--- a/diseases/d007/2000-2004.xlsx
+++ b/diseases/d007/2000-2004.xlsx
@@ -42216,7 +42216,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -43700,7 +43700,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45184,7 +45184,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -46668,7 +46668,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -48152,7 +48152,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -49636,7 +49636,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -51120,7 +51120,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -52604,7 +52604,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -54088,7 +54088,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -55572,7 +55572,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -57056,7 +57056,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -58540,7 +58540,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -60263,7 +60263,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -61747,7 +61747,7 @@
       </c>
       <c r="AJ334" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK334" t="inlineStr">
@@ -63231,7 +63231,7 @@
       </c>
       <c r="AJ342" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK342" t="inlineStr">
@@ -64715,7 +64715,7 @@
       </c>
       <c r="AJ350" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK350" t="inlineStr">
@@ -66199,7 +66199,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -67683,7 +67683,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -69167,7 +69167,7 @@
       </c>
       <c r="AJ374" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK374" t="inlineStr">
@@ -70651,7 +70651,7 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -72135,7 +72135,7 @@
       </c>
       <c r="AJ390" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK390" t="inlineStr">
@@ -73619,7 +73619,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -75103,7 +75103,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -76587,7 +76587,7 @@
       </c>
       <c r="AJ414" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK414" t="inlineStr">

--- a/diseases/d007/2000-2004.xlsx
+++ b/diseases/d007/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -1696,9 +1693,6 @@
       <c r="O7" t="n">
         <v>23</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.5121505491033246</v>
       </c>
@@ -2240,9 +2234,6 @@
       <c r="O10" t="n">
         <v>4</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -2784,9 +2775,6 @@
       <c r="O13" t="n">
         <v>9</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.2004067366056487</v>
       </c>
@@ -3328,9 +3316,6 @@
       <c r="O16" t="n">
         <v>4</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -3872,9 +3857,6 @@
       <c r="O19" t="n">
         <v>11</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.2449415669624596</v>
       </c>
@@ -4416,9 +4398,6 @@
       <c r="O22" t="n">
         <v>3</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -4960,9 +4939,6 @@
       <c r="O25" t="n">
         <v>7</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.1558719062488379</v>
       </c>
@@ -5504,9 +5480,6 @@
       <c r="O28" t="n">
         <v>5</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -6048,9 +6021,6 @@
       <c r="O31" t="n">
         <v>6</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.1336044910704325</v>
       </c>
@@ -6592,9 +6562,6 @@
       <c r="O34" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -7136,9 +7103,6 @@
       <c r="O37" t="n">
         <v>11</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.2449415669624596</v>
       </c>
@@ -7680,9 +7644,6 @@
       <c r="O40" t="n">
         <v>5</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -8224,9 +8185,6 @@
       <c r="O43" t="n">
         <v>26</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.5789527946385408</v>
       </c>
@@ -8768,9 +8726,6 @@
       <c r="O46" t="n">
         <v>8</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.1545534886924321</v>
       </c>
@@ -9312,9 +9267,6 @@
       <c r="O49" t="n">
         <v>8</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.1781393214272433</v>
       </c>
@@ -9856,9 +9808,6 @@
       <c r="O52" t="n">
         <v>5</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -10400,9 +10349,6 @@
       <c r="O55" t="n">
         <v>25</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.5566853794601354</v>
       </c>
@@ -10944,9 +10890,6 @@
       <c r="O58" t="n">
         <v>3</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -11488,9 +11431,6 @@
       <c r="O61" t="n">
         <v>14</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.3117438124976759</v>
       </c>
@@ -12032,9 +11972,6 @@
       <c r="O64" t="n">
         <v>5</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -12576,9 +12513,6 @@
       <c r="O67" t="n">
         <v>6</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.1336044910704325</v>
       </c>
@@ -13120,9 +13054,6 @@
       <c r="O70" t="n">
         <v>5</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -13664,9 +13595,6 @@
       <c r="O73" t="n">
         <v>13</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.2894763973192704</v>
       </c>
@@ -14208,9 +14136,6 @@
       <c r="O76" t="n">
         <v>5</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -14991,9 +14916,6 @@
       <c r="O80" t="n">
         <v>3</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.0664649529195506</v>
       </c>
@@ -15535,9 +15457,6 @@
       <c r="O83" t="n">
         <v>6</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.1156521499445544</v>
       </c>
@@ -16079,9 +15998,6 @@
       <c r="O86" t="n">
         <v>7</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.1550848901456181</v>
       </c>
@@ -16623,9 +16539,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -17167,9 +17080,6 @@
       <c r="O92" t="n">
         <v>3</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.0664649529195506</v>
       </c>
@@ -17711,9 +17621,6 @@
       <c r="O95" t="n">
         <v>3</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -18255,9 +18162,6 @@
       <c r="O98" t="n">
         <v>3</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.0664649529195506</v>
       </c>
@@ -18799,9 +18703,6 @@
       <c r="O101" t="n">
         <v>7</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.1349275082686468</v>
       </c>
@@ -19343,9 +19244,6 @@
       <c r="O104" t="n">
         <v>6</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.1329299058391012</v>
       </c>
@@ -19887,9 +19785,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -20431,9 +20326,6 @@
       <c r="O110" t="n">
         <v>5</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.1107749215325843</v>
       </c>
@@ -20975,9 +20867,6 @@
       <c r="O113" t="n">
         <v>6</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.1156521499445544</v>
       </c>
@@ -21519,9 +21408,6 @@
       <c r="O116" t="n">
         <v>9</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.1993948587586518</v>
       </c>
@@ -22063,9 +21949,6 @@
       <c r="O119" t="n">
         <v>5</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -22607,9 +22490,6 @@
       <c r="O122" t="n">
         <v>10</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.2215498430651687</v>
       </c>
@@ -23151,9 +23031,6 @@
       <c r="O125" t="n">
         <v>4</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.07710143329636962</v>
       </c>
@@ -23695,9 +23572,6 @@
       <c r="O128" t="n">
         <v>12</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.2658598116782024</v>
       </c>
@@ -24239,9 +24113,6 @@
       <c r="O131" t="n">
         <v>5</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -24783,9 +24654,6 @@
       <c r="O134" t="n">
         <v>12</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.2658598116782024</v>
       </c>
@@ -25327,9 +25195,6 @@
       <c r="O137" t="n">
         <v>4</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.07710143329636962</v>
       </c>
@@ -25871,9 +25736,6 @@
       <c r="O140" t="n">
         <v>9</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.1993948587586518</v>
       </c>
@@ -26415,9 +26277,6 @@
       <c r="O143" t="n">
         <v>5</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -26959,9 +26818,6 @@
       <c r="O146" t="n">
         <v>6</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.1329299058391012</v>
       </c>
@@ -27503,9 +27359,6 @@
       <c r="O149" t="n">
         <v>17</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.3268887536039485</v>
       </c>
@@ -28286,9 +28139,6 @@
       <c r="O153" t="n">
         <v>2</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -28830,9 +28680,6 @@
       <c r="O156" t="n">
         <v>15</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.2884312531799545</v>
       </c>
@@ -29374,9 +29221,6 @@
       <c r="O159" t="n">
         <v>4</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -29918,9 +29762,6 @@
       <c r="O162" t="n">
         <v>25</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.4807187552999243</v>
       </c>
@@ -30462,9 +30303,6 @@
       <c r="O165" t="n">
         <v>1</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -31006,9 +30844,6 @@
       <c r="O168" t="n">
         <v>36</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.6922350076318909</v>
       </c>
@@ -31550,9 +31385,6 @@
       <c r="O171" t="n">
         <v>9</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.1983246415722825</v>
       </c>
@@ -32094,9 +31926,6 @@
       <c r="O174" t="n">
         <v>40</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.7691500084798788</v>
       </c>
@@ -32638,9 +32467,6 @@
       <c r="O177" t="n">
         <v>2</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -33182,9 +33008,6 @@
       <c r="O180" t="n">
         <v>25</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.4807187552999243</v>
       </c>
@@ -33726,9 +33549,6 @@
       <c r="O183" t="n">
         <v>4</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -34270,9 +34090,6 @@
       <c r="O186" t="n">
         <v>34</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.6537775072078971</v>
       </c>
@@ -34814,9 +34631,6 @@
       <c r="O189" t="n">
         <v>10</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.2203607128580917</v>
       </c>
@@ -35358,9 +35172,6 @@
       <c r="O192" t="n">
         <v>45</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.8652937595398636</v>
       </c>
@@ -35902,9 +35713,6 @@
       <c r="O195" t="n">
         <v>7</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.1542524990006642</v>
       </c>
@@ -36446,9 +36254,6 @@
       <c r="O198" t="n">
         <v>43</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.8268362591158698</v>
       </c>
@@ -36990,9 +36795,6 @@
       <c r="O201" t="n">
         <v>13</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.2864689267155192</v>
       </c>
@@ -37534,9 +37336,6 @@
       <c r="O204" t="n">
         <v>48</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.9229800101758546</v>
       </c>
@@ -38078,9 +37877,6 @@
       <c r="O207" t="n">
         <v>13</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.2864689267155192</v>
       </c>
@@ -38622,9 +38418,6 @@
       <c r="O210" t="n">
         <v>27</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.5191762557239182</v>
       </c>
@@ -39166,9 +38959,6 @@
       <c r="O213" t="n">
         <v>4</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -39710,9 +39500,6 @@
       <c r="O216" t="n">
         <v>37</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.7114637578438879</v>
       </c>
@@ -40254,9 +40041,6 @@
       <c r="O219" t="n">
         <v>5</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.1101803564290458</v>
       </c>
@@ -40798,9 +40582,6 @@
       <c r="O222" t="n">
         <v>44</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.8440510228843334</v>
       </c>
@@ -41581,9 +41362,6 @@
       <c r="O226" t="n">
         <v>5</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.1095369675216319</v>
       </c>
@@ -42226,7 +42004,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -42521,9 +42299,6 @@
       <c r="O231" t="n">
         <v>20</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.3836595558565151</v>
       </c>
@@ -43065,9 +42840,6 @@
       <c r="O234" t="n">
         <v>9</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.1971665415389375</v>
       </c>
@@ -43710,7 +43482,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -44005,9 +43777,6 @@
       <c r="O239" t="n">
         <v>15</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.2877446668923864</v>
       </c>
@@ -44549,9 +44318,6 @@
       <c r="O242" t="n">
         <v>1</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -45194,7 +44960,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -45489,9 +45255,6 @@
       <c r="O247" t="n">
         <v>3</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -46033,9 +45796,6 @@
       <c r="O250" t="n">
         <v>2</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -46678,7 +46438,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -46973,9 +46733,6 @@
       <c r="O255" t="n">
         <v>23</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.4412084892349924</v>
       </c>
@@ -47517,9 +47274,6 @@
       <c r="O258" t="n">
         <v>4</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -48162,7 +47916,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -48457,9 +48211,6 @@
       <c r="O263" t="n">
         <v>30</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.5754893337847727</v>
       </c>
@@ -49001,9 +48752,6 @@
       <c r="O266" t="n">
         <v>4</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -49646,7 +49394,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -49941,9 +49689,6 @@
       <c r="O271" t="n">
         <v>31</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.5946723115775985</v>
       </c>
@@ -50485,9 +50230,6 @@
       <c r="O274" t="n">
         <v>7</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.1533517545302847</v>
       </c>
@@ -51130,7 +50872,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -51425,9 +51167,6 @@
       <c r="O279" t="n">
         <v>32</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.6138552893704243</v>
       </c>
@@ -51969,9 +51708,6 @@
       <c r="O282" t="n">
         <v>3</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.06572218051297914</v>
       </c>
@@ -52614,7 +52350,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -52909,9 +52645,6 @@
       <c r="O287" t="n">
         <v>27</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.5179404004062954</v>
       </c>
@@ -53453,9 +53186,6 @@
       <c r="O290" t="n">
         <v>7</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.1533517545302847</v>
       </c>
@@ -54098,7 +53828,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -54393,9 +54123,6 @@
       <c r="O295" t="n">
         <v>11</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.2110127557210834</v>
       </c>
@@ -54937,9 +54664,6 @@
       <c r="O298" t="n">
         <v>15</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0.3286109025648957</v>
       </c>
@@ -55582,7 +55306,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -55877,9 +55601,6 @@
       <c r="O303" t="n">
         <v>2</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -56421,9 +56142,6 @@
       <c r="O306" t="n">
         <v>10</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.2190739350432638</v>
       </c>
@@ -57066,7 +56784,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -57361,9 +57079,6 @@
       <c r="O311" t="n">
         <v>5</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -57905,9 +57620,6 @@
       <c r="O314" t="n">
         <v>11</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0.2409813285475902</v>
       </c>
@@ -58550,7 +58262,7 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -58845,9 +58557,6 @@
       <c r="O319" t="n">
         <v>11</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>0.2103995525757878</v>
       </c>
@@ -59628,9 +59337,6 @@
       <c r="O323" t="n">
         <v>3</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -60273,7 +59979,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -60568,9 +60274,6 @@
       <c r="O328" t="n">
         <v>1</v>
       </c>
-      <c r="Q328" t="n">
-        <v>0</v>
-      </c>
       <c r="R328" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -61112,9 +60815,6 @@
       <c r="O331" t="n">
         <v>7</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0.152447573007415</v>
       </c>
@@ -61757,7 +61457,7 @@
       </c>
       <c r="AM334" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN334" t="b">
@@ -62052,9 +61752,6 @@
       <c r="O336" t="n">
         <v>3</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -62596,9 +62293,6 @@
       <c r="O339" t="n">
         <v>9</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0.1960040224381049</v>
       </c>
@@ -63241,7 +62935,7 @@
       </c>
       <c r="AM342" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN342" t="b">
@@ -63536,9 +63230,6 @@
       <c r="O344" t="n">
         <v>1</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -64080,9 +63771,6 @@
       <c r="O347" t="n">
         <v>10</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0.2177822471534499</v>
       </c>
@@ -64725,7 +64413,7 @@
       </c>
       <c r="AM350" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN350" t="b">
@@ -65020,9 +64708,6 @@
       <c r="O352" t="n">
         <v>1</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -65564,9 +65249,6 @@
       <c r="O355" t="n">
         <v>4</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -66209,7 +65891,7 @@
       </c>
       <c r="AM358" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN358" t="b">
@@ -66504,9 +66186,6 @@
       <c r="O360" t="n">
         <v>2</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -67048,9 +66727,6 @@
       <c r="O363" t="n">
         <v>7</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0.152447573007415</v>
       </c>
@@ -67693,7 +67369,7 @@
       </c>
       <c r="AM366" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN366" t="b">
@@ -67988,9 +67664,6 @@
       <c r="O368" t="n">
         <v>2</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -68532,9 +68205,6 @@
       <c r="O371" t="n">
         <v>33</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0.7186814156063848</v>
       </c>
@@ -69177,7 +68847,7 @@
       </c>
       <c r="AM374" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN374" t="b">
@@ -69472,9 +69142,6 @@
       <c r="O376" t="n">
         <v>6</v>
       </c>
-      <c r="Q376" t="n">
-        <v>0</v>
-      </c>
       <c r="R376" t="n">
         <v>0.1147633923140661</v>
       </c>
@@ -70016,9 +69683,6 @@
       <c r="O379" t="n">
         <v>38</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0.8275725391831097</v>
       </c>
@@ -70661,7 +70325,7 @@
       </c>
       <c r="AM382" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN382" t="b">
@@ -70956,9 +70620,6 @@
       <c r="O384" t="n">
         <v>4</v>
       </c>
-      <c r="Q384" t="n">
-        <v>0</v>
-      </c>
       <c r="R384" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -71500,9 +71161,6 @@
       <c r="O387" t="n">
         <v>31</v>
       </c>
-      <c r="Q387" t="n">
-        <v>0</v>
-      </c>
       <c r="R387" t="n">
         <v>0.6751249661756947</v>
       </c>
@@ -72145,7 +71803,7 @@
       </c>
       <c r="AM390" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN390" t="b">
@@ -72440,9 +72098,6 @@
       <c r="O392" t="n">
         <v>3</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -72984,9 +72639,6 @@
       <c r="O395" t="n">
         <v>20</v>
       </c>
-      <c r="Q395" t="n">
-        <v>0</v>
-      </c>
       <c r="R395" t="n">
         <v>0.4355644943068998</v>
       </c>
@@ -73629,7 +73281,7 @@
       </c>
       <c r="AM398" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN398" t="b">
@@ -73924,9 +73576,6 @@
       <c r="O400" t="n">
         <v>4</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -74468,9 +74117,6 @@
       <c r="O403" t="n">
         <v>11</v>
       </c>
-      <c r="Q403" t="n">
-        <v>0</v>
-      </c>
       <c r="R403" t="n">
         <v>0.2395604718687949</v>
       </c>
@@ -75113,7 +74759,7 @@
       </c>
       <c r="AM406" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN406" t="b">
@@ -75408,9 +75054,6 @@
       <c r="O408" t="n">
         <v>4</v>
       </c>
-      <c r="Q408" t="n">
-        <v>0</v>
-      </c>
       <c r="R408" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -75952,9 +75595,6 @@
       <c r="O411" t="n">
         <v>7</v>
       </c>
-      <c r="Q411" t="n">
-        <v>0</v>
-      </c>
       <c r="R411" t="n">
         <v>0.152447573007415</v>
       </c>
@@ -76597,7 +76237,7 @@
       </c>
       <c r="AM414" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN414" t="b">

--- a/diseases/d007/2000-2004.xlsx
+++ b/diseases/d007/2000-2004.xlsx
@@ -41994,7 +41994,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -43472,7 +43472,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -44950,7 +44950,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -46428,7 +46428,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -47906,7 +47906,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -49384,7 +49384,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -50862,7 +50862,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -52340,7 +52340,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -53818,7 +53818,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -55296,7 +55296,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -56774,7 +56774,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -58252,7 +58252,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -59969,7 +59969,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -61447,7 +61447,7 @@
       </c>
       <c r="AJ334" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK334" t="inlineStr">
@@ -62925,7 +62925,7 @@
       </c>
       <c r="AJ342" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK342" t="inlineStr">
@@ -64403,7 +64403,7 @@
       </c>
       <c r="AJ350" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK350" t="inlineStr">
@@ -65881,7 +65881,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -67359,7 +67359,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -68837,7 +68837,7 @@
       </c>
       <c r="AJ374" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK374" t="inlineStr">
@@ -70315,7 +70315,7 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -71793,7 +71793,7 @@
       </c>
       <c r="AJ390" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK390" t="inlineStr">
@@ -73271,7 +73271,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -74749,7 +74749,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -76227,7 +76227,7 @@
       </c>
       <c r="AJ414" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK414" t="inlineStr">

--- a/diseases/d007/2000-2004.xlsx
+++ b/diseases/d007/2000-2004.xlsx
@@ -41994,7 +41994,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -43472,7 +43472,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -44950,7 +44950,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -46428,7 +46428,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -47906,7 +47906,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -49384,7 +49384,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -50862,7 +50862,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -52340,7 +52340,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -53818,7 +53818,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -55296,7 +55296,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -56774,7 +56774,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -58252,7 +58252,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -59969,7 +59969,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -61447,7 +61447,7 @@
       </c>
       <c r="AJ334" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK334" t="inlineStr">
@@ -62925,7 +62925,7 @@
       </c>
       <c r="AJ342" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK342" t="inlineStr">
@@ -64403,7 +64403,7 @@
       </c>
       <c r="AJ350" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK350" t="inlineStr">
@@ -65881,7 +65881,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -67359,7 +67359,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -68837,7 +68837,7 @@
       </c>
       <c r="AJ374" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK374" t="inlineStr">
@@ -70315,7 +70315,7 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -71793,7 +71793,7 @@
       </c>
       <c r="AJ390" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK390" t="inlineStr">
@@ -73271,7 +73271,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -74749,7 +74749,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -76227,7 +76227,7 @@
       </c>
       <c r="AJ414" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK414" t="inlineStr">

--- a/diseases/d007/2000-2004.xlsx
+++ b/diseases/d007/2000-2004.xlsx
@@ -41994,7 +41994,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -43472,7 +43472,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -44950,7 +44950,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -46428,7 +46428,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -47906,7 +47906,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -49384,7 +49384,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -50862,7 +50862,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -52340,7 +52340,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -53818,7 +53818,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -55296,7 +55296,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -56774,7 +56774,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -58252,7 +58252,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -59969,7 +59969,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -61447,7 +61447,7 @@
       </c>
       <c r="AJ334" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK334" t="inlineStr">
@@ -62925,7 +62925,7 @@
       </c>
       <c r="AJ342" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK342" t="inlineStr">
@@ -64403,7 +64403,7 @@
       </c>
       <c r="AJ350" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK350" t="inlineStr">
@@ -65881,7 +65881,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -67359,7 +67359,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -68837,7 +68837,7 @@
       </c>
       <c r="AJ374" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK374" t="inlineStr">
@@ -70315,7 +70315,7 @@
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -71793,7 +71793,7 @@
       </c>
       <c r="AJ390" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK390" t="inlineStr">
@@ -73271,7 +73271,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -74749,7 +74749,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -76227,7 +76227,7 @@
       </c>
       <c r="AJ414" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK414" t="inlineStr">
